--- a/A_Main_Code/Outcome/Results_n100.xlsx
+++ b/A_Main_Code/Outcome/Results_n100.xlsx
@@ -57,2566 +57,2566 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.453125" customWidth="true"/>
-    <col min="2" max="2" width="14.453125" customWidth="true"/>
+    <col min="2" max="2" width="14.08984375" customWidth="true"/>
     <col min="3" max="3" width="12.453125" customWidth="true"/>
     <col min="4" max="4" width="12.453125" customWidth="true"/>
-    <col min="5" max="5" width="14.08984375" customWidth="true"/>
+    <col min="5" max="5" width="14.453125" customWidth="true"/>
     <col min="6" max="6" width="12.453125" customWidth="true"/>
     <col min="7" max="7" width="16.08984375" customWidth="true"/>
     <col min="8" max="8" width="16.08984375" customWidth="true"/>
-    <col min="9" max="9" width="15.08984375" customWidth="true"/>
+    <col min="9" max="9" width="15.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0.19674358982683601</v>
+        <v>0.20023874594077301</v>
       </c>
       <c r="B1" s="0">
-        <v>-0.15448404587162201</v>
+        <v>-0.16782691085974399</v>
       </c>
       <c r="C1" s="0">
-        <v>0.30327980621324002</v>
+        <v>0.28376351646647402</v>
       </c>
       <c r="D1" s="0">
-        <v>0.21318962766893176</v>
+        <v>0.21049637158867673</v>
       </c>
       <c r="E1" s="0">
-        <v>-0.094803607211193713</v>
+        <v>-0.10945738413833853</v>
       </c>
       <c r="F1" s="0">
-        <v>0.28959872652733565</v>
+        <v>0.23384072091415653</v>
       </c>
       <c r="G1" s="0">
-        <v>-0.016322839265289681</v>
+        <v>-0.011825148897697695</v>
       </c>
       <c r="H1" s="0">
-        <v>-0.058292893465757875</v>
+        <v>-0.056907636661889416</v>
       </c>
       <c r="I1" s="0">
-        <v>0.013178052372495957</v>
+        <v>0.050357542179487798</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.232886317181623</v>
+        <v>0.23034872416473601</v>
       </c>
       <c r="B2" s="0">
-        <v>-0.098656248818357203</v>
+        <v>-0.10513365942243</v>
       </c>
       <c r="C2" s="0">
-        <v>0.34317058377056803</v>
+        <v>0.34712252425143297</v>
       </c>
       <c r="D2" s="0">
-        <v>0.24731108178776864</v>
+        <v>0.244079427211078</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.058680446616349219</v>
+        <v>-0.071824419930305181</v>
       </c>
       <c r="F2" s="0">
-        <v>0.31571925791457889</v>
+        <v>0.26192945345956259</v>
       </c>
       <c r="G2" s="0">
-        <v>-0.016407633673237835</v>
+        <v>-0.013986970407265244</v>
       </c>
       <c r="H2" s="0">
-        <v>-0.04089056806736853</v>
+        <v>-0.034363858269620851</v>
       </c>
       <c r="I2" s="0">
-        <v>0.029513547856030171</v>
+        <v>0.085720849347897851</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.26218843085335602</v>
+        <v>0.26385127861135799</v>
       </c>
       <c r="B3" s="0">
-        <v>-0.0464047738771107</v>
+        <v>-0.049162017109316898</v>
       </c>
       <c r="C3" s="0">
-        <v>0.39669844705586499</v>
+        <v>0.40215512011849203</v>
       </c>
       <c r="D3" s="0">
-        <v>0.28091630487174996</v>
+        <v>0.27766292701710349</v>
       </c>
       <c r="E3" s="0">
-        <v>-0.023102523112019529</v>
+        <v>-0.034944984101496601</v>
       </c>
       <c r="F3" s="0">
-        <v>0.34223364031866149</v>
+        <v>0.28995044712050128</v>
       </c>
       <c r="G3" s="0">
-        <v>-0.016556604492503596</v>
+        <v>-0.014032136906065841</v>
       </c>
       <c r="H3" s="0">
-        <v>-0.022921367517167217</v>
+        <v>-0.010564118641030979</v>
       </c>
       <c r="I3" s="0">
-        <v>0.051571549792274581</v>
+        <v>0.11018158563624256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.299754753755406</v>
+        <v>0.29786731940736699</v>
       </c>
       <c r="B4" s="0">
-        <v>0.0038496210259159401</v>
+        <v>0.020267376723266201</v>
       </c>
       <c r="C4" s="0">
-        <v>0.41700324504947101</v>
+        <v>0.42448056699930697</v>
       </c>
       <c r="D4" s="0">
-        <v>0.31495042254749811</v>
+        <v>0.31037271973134561</v>
       </c>
       <c r="E4" s="0">
-        <v>0.011470988937341459</v>
+        <v>0.0016616374508065951</v>
       </c>
       <c r="F4" s="0">
-        <v>0.36796757912896405</v>
+        <v>0.31757277656468363</v>
       </c>
       <c r="G4" s="0">
-        <v>-0.016052042797175231</v>
+        <v>-0.0094547045742431595</v>
       </c>
       <c r="H4" s="0">
-        <v>-0.0081210938240437597</v>
+        <v>0.010689712569200741</v>
       </c>
       <c r="I4" s="0">
-        <v>0.049753983011345683</v>
+        <v>0.10597499384386469</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.33402569579128999</v>
+        <v>0.33620861755255099</v>
       </c>
       <c r="B5" s="0">
-        <v>0.048392791221753502</v>
+        <v>0.041815473637286001</v>
       </c>
       <c r="C5" s="0">
-        <v>0.44170294793562898</v>
+        <v>0.42913979327794499</v>
       </c>
       <c r="D5" s="0">
-        <v>0.34861811829734207</v>
+        <v>0.345126682777816</v>
       </c>
       <c r="E5" s="0">
-        <v>0.044888040894980684</v>
+        <v>0.034283739770032122</v>
       </c>
       <c r="F5" s="0">
-        <v>0.39377916920822742</v>
+        <v>0.34428069188641003</v>
       </c>
       <c r="G5" s="0">
-        <v>-0.015265116317644984</v>
+        <v>-0.011081330694230666</v>
       </c>
       <c r="H5" s="0">
-        <v>0.0011565409627551785</v>
+        <v>0.0092598177622226149</v>
       </c>
       <c r="I5" s="0">
-        <v>0.049591651961271549</v>
+        <v>0.089131199743339898</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.36044752058660701</v>
+        <v>0.35839847508406503</v>
       </c>
       <c r="B6" s="0">
-        <v>0.080371852557594506</v>
+        <v>0.073896771144341206</v>
       </c>
       <c r="C6" s="0">
-        <v>0.48581420281010601</v>
+        <v>0.485434735754947</v>
       </c>
       <c r="D6" s="0">
-        <v>0.38229802613255709</v>
+        <v>0.37856715724319184</v>
       </c>
       <c r="E6" s="0">
-        <v>0.076760596881004256</v>
+        <v>0.066746626291896038</v>
       </c>
       <c r="F6" s="0">
-        <v>0.4198229256140586</v>
+        <v>0.37215391344312282</v>
       </c>
       <c r="G6" s="0">
-        <v>-0.013585207619951837</v>
+        <v>-0.011461613021907938</v>
       </c>
       <c r="H6" s="0">
-        <v>0.0055753963127587068</v>
+        <v>0.01062422868048926</v>
       </c>
       <c r="I6" s="0">
-        <v>0.064964620337764831</v>
+        <v>0.11111109241891193</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.41716297753982301</v>
+        <v>0.41874846618726402</v>
       </c>
       <c r="B7" s="0">
-        <v>0.123242604680055</v>
+        <v>0.12347344192192</v>
       </c>
       <c r="C7" s="0">
-        <v>0.52792995599239401</v>
+        <v>0.533019213669641</v>
       </c>
       <c r="D7" s="0">
-        <v>0.41714026785095654</v>
+        <v>0.41318722747555908</v>
       </c>
       <c r="E7" s="0">
-        <v>0.10801752699137482</v>
+        <v>0.099312777753844422</v>
       </c>
       <c r="F7" s="0">
-        <v>0.44547876813541903</v>
+        <v>0.39952669405174285</v>
       </c>
       <c r="G7" s="0">
-        <v>-0.002569235671838652</v>
+        <v>0.00099245962939909969</v>
       </c>
       <c r="H7" s="0">
-        <v>0.014025374443923747</v>
+        <v>0.023321732383577737</v>
       </c>
       <c r="I7" s="0">
-        <v>0.082182009345264415</v>
+        <v>0.1332387839964618</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.45844238755400502</v>
+        <v>0.45734870530444699</v>
       </c>
       <c r="B8" s="0">
-        <v>0.16017855638906001</v>
+        <v>0.169692817500186</v>
       </c>
       <c r="C8" s="0">
-        <v>0.56698441771276398</v>
+        <v>0.57257772614958602</v>
       </c>
       <c r="D8" s="0">
-        <v>0.45157955778230818</v>
+        <v>0.44693897468412586</v>
       </c>
       <c r="E8" s="0">
-        <v>0.13864929933546002</v>
+        <v>0.13135231145054771</v>
       </c>
       <c r="F8" s="0">
-        <v>0.47096961076410654</v>
+        <v>0.42676002099617522</v>
       </c>
       <c r="G8" s="0">
-        <v>0.0077322926601216396</v>
+        <v>0.013727204292769496</v>
       </c>
       <c r="H8" s="0">
-        <v>0.021002504728804688</v>
+        <v>0.033527096398254942</v>
       </c>
       <c r="I8" s="0">
-        <v>0.096941335192000391</v>
+        <v>0.14526735171740435</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.50379797465111298</v>
+        <v>0.50477841163818304</v>
       </c>
       <c r="B9" s="0">
-        <v>0.195046692840042</v>
+        <v>0.19027303383254501</v>
       </c>
       <c r="C9" s="0">
-        <v>0.61205597258352196</v>
+        <v>0.60023807713242605</v>
       </c>
       <c r="D9" s="0">
-        <v>0.48599496990737795</v>
+        <v>0.48215368021628019</v>
       </c>
       <c r="E9" s="0">
-        <v>0.16903958615953413</v>
+        <v>0.16144493269425531</v>
       </c>
       <c r="F9" s="0">
-        <v>0.49642104374792806</v>
+        <v>0.45324956142859185</v>
       </c>
       <c r="G9" s="0">
-        <v>0.017809774202078247</v>
+        <v>0.021717433262024393</v>
       </c>
       <c r="H9" s="0">
-        <v>0.032166763101292267</v>
+        <v>0.037551303583031451</v>
       </c>
       <c r="I9" s="0">
-        <v>0.11382524336521357</v>
+        <v>0.1478620529782709</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.55411535214324703</v>
+        <v>0.55264621547668502</v>
       </c>
       <c r="B10" s="0">
-        <v>0.26216525174025701</v>
+        <v>0.25827593079720901</v>
       </c>
       <c r="C10" s="0">
-        <v>0.63986439682222496</v>
+        <v>0.64141637180399302</v>
       </c>
       <c r="D10" s="0">
-        <v>0.51894902842281898</v>
+        <v>0.51499003807872024</v>
       </c>
       <c r="E10" s="0">
-        <v>0.20080650628460975</v>
+        <v>0.19383210105566551</v>
       </c>
       <c r="F10" s="0">
-        <v>0.52162061904609247</v>
+        <v>0.48030628996764968</v>
       </c>
       <c r="G10" s="0">
-        <v>0.032062672660250473</v>
+        <v>0.035039763000998578</v>
       </c>
       <c r="H10" s="0">
-        <v>0.053621179984308917</v>
+        <v>0.057785216661284208</v>
       </c>
       <c r="I10" s="0">
-        <v>0.11880743558776351</v>
+        <v>0.16024838272028499</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.58616838773733504</v>
+        <v>0.58759732458279301</v>
       </c>
       <c r="B11" s="0">
-        <v>0.28869610613529301</v>
+        <v>0.29046965486757398</v>
       </c>
       <c r="C11" s="0">
-        <v>0.665249844896589</v>
+        <v>0.66956147655611797</v>
       </c>
       <c r="D11" s="0">
-        <v>0.55233097858973168</v>
+        <v>0.54834322253444456</v>
       </c>
       <c r="E11" s="0">
-        <v>0.22994613198136954</v>
+        <v>0.22396490497867291</v>
       </c>
       <c r="F11" s="0">
-        <v>0.54623786875486924</v>
+        <v>0.50654980536313099</v>
       </c>
       <c r="G11" s="0">
-        <v>0.036712517753898603</v>
+        <v>0.04095001983478478</v>
       </c>
       <c r="H11" s="0">
-        <v>0.062084309686030917</v>
+        <v>0.069156321484224403</v>
       </c>
       <c r="I11" s="0">
-        <v>0.12017279928678376</v>
+        <v>0.16436341671477273</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.62732967235416204</v>
+        <v>0.62690332116139103</v>
       </c>
       <c r="B12" s="0">
-        <v>0.33663108801864799</v>
+        <v>0.340760971460633</v>
       </c>
       <c r="C12" s="0">
-        <v>0.70730451009539197</v>
+        <v>0.71145041655287</v>
       </c>
       <c r="D12" s="0">
-        <v>0.58489542328946453</v>
+        <v>0.58076197968727716</v>
       </c>
       <c r="E12" s="0">
-        <v>0.25933914569434124</v>
+        <v>0.25411172126213238</v>
       </c>
       <c r="F12" s="0">
-        <v>0.57094882483363552</v>
+        <v>0.53285820536024242</v>
       </c>
       <c r="G12" s="0">
-        <v>0.043473032305188383</v>
+        <v>0.048396745521373533</v>
       </c>
       <c r="H12" s="0">
-        <v>0.077975095482133064</v>
+        <v>0.085664396214515687</v>
       </c>
       <c r="I12" s="0">
-        <v>0.13650586983924873</v>
+        <v>0.17791663752198897</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.67779544726635299</v>
+        <v>0.67790048769782596</v>
       </c>
       <c r="B13" s="0">
-        <v>0.386096116561158</v>
+        <v>0.38323885338108898</v>
       </c>
       <c r="C13" s="0">
-        <v>0.74929023344865697</v>
+        <v>0.74315635716149098</v>
       </c>
       <c r="D13" s="0">
-        <v>0.61686781651756473</v>
+        <v>0.61324052744086721</v>
       </c>
       <c r="E13" s="0">
-        <v>0.28846757101072562</v>
+        <v>0.2832446774122519</v>
       </c>
       <c r="F13" s="0">
-        <v>0.59531171990781184</v>
+        <v>0.55845851080109876</v>
       </c>
       <c r="G13" s="0">
-        <v>0.053404576681068933</v>
+        <v>0.056681704852050388</v>
       </c>
       <c r="H13" s="0">
-        <v>0.098341977489019197</v>
+        <v>0.1021061022941923</v>
       </c>
       <c r="I13" s="0">
-        <v>0.15227391720613295</v>
+        <v>0.18419072134364894</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.70165446410029997</v>
+        <v>0.70053425007842396</v>
       </c>
       <c r="B14" s="0">
-        <v>0.43347544617966499</v>
+        <v>0.43159540564891602</v>
       </c>
       <c r="C14" s="0">
-        <v>0.76625022615562199</v>
+        <v>0.76468422328394403</v>
       </c>
       <c r="D14" s="0">
-        <v>0.64655537127121032</v>
+        <v>0.64297705337524202</v>
       </c>
       <c r="E14" s="0">
-        <v>0.3172705835043042</v>
+        <v>0.31254641956396934</v>
       </c>
       <c r="F14" s="0">
-        <v>0.61905470582877498</v>
+        <v>0.58382012655200166</v>
       </c>
       <c r="G14" s="0">
-        <v>0.060654684254242246</v>
+        <v>0.063455423669336389</v>
       </c>
       <c r="H14" s="0">
-        <v>0.11488579523696295</v>
+        <v>0.11828302002439559</v>
       </c>
       <c r="I14" s="0">
-        <v>0.14756983596770185</v>
+        <v>0.18102297748180007</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.74788792010609295</v>
+        <v>0.74916827329986602</v>
       </c>
       <c r="B15" s="0">
-        <v>0.469006886291787</v>
+        <v>0.47108416191451502</v>
       </c>
       <c r="C15" s="0">
-        <v>0.79553205442262998</v>
+        <v>0.79856967775572896</v>
       </c>
       <c r="D15" s="0">
-        <v>0.67660162019154146</v>
+        <v>0.67308251735977365</v>
       </c>
       <c r="E15" s="0">
-        <v>0.34418114619460916</v>
+        <v>0.34012692208905904</v>
       </c>
       <c r="F15" s="0">
-        <v>0.64206846959941222</v>
+        <v>0.60843620158803902</v>
       </c>
       <c r="G15" s="0">
-        <v>0.069961598319150969</v>
+        <v>0.074003306654168363</v>
       </c>
       <c r="H15" s="0">
-        <v>0.12220394697541423</v>
+        <v>0.12746234741287218</v>
       </c>
       <c r="I15" s="0">
-        <v>0.14002734966826177</v>
+        <v>0.17659117026076371</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.77853048182134299</v>
+        <v>0.778472915352863</v>
       </c>
       <c r="B16" s="0">
-        <v>0.48546257128249098</v>
+        <v>0.48678196137650298</v>
       </c>
       <c r="C16" s="0">
-        <v>0.80490519195402399</v>
+        <v>0.80847990315871399</v>
       </c>
       <c r="D16" s="0">
-        <v>0.70587142631071875</v>
+        <v>0.70243982384159376</v>
       </c>
       <c r="E16" s="0">
-        <v>0.36929474970933163</v>
+        <v>0.36559419254215358</v>
       </c>
       <c r="F16" s="0">
-        <v>0.64717895544371795</v>
+        <v>0.61503695127911773</v>
       </c>
       <c r="G16" s="0">
-        <v>0.072351276024041469</v>
+        <v>0.076275122243582516</v>
       </c>
       <c r="H16" s="0">
-        <v>0.11763466485602447</v>
+        <v>0.12234629463026658</v>
       </c>
       <c r="I16" s="0">
-        <v>0.14130874034233054</v>
+        <v>0.17618874958833891</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>0.804068958724102</v>
+        <v>0.80381871046684905</v>
       </c>
       <c r="B17" s="0">
-        <v>0.50635254618450698</v>
+        <v>0.50464106245093698</v>
       </c>
       <c r="C17" s="0">
-        <v>0.82225868565211602</v>
+        <v>0.81729782288422803</v>
       </c>
       <c r="D17" s="0">
-        <v>0.73374835127699567</v>
+        <v>0.73064739939634638</v>
       </c>
       <c r="E17" s="0">
-        <v>0.39425052577685871</v>
+        <v>0.39065284719716509</v>
       </c>
       <c r="F17" s="0">
-        <v>0.66952579351948438</v>
+        <v>0.63861323028080175</v>
       </c>
       <c r="G17" s="0">
-        <v>0.070082847695995015</v>
+        <v>0.07265724271069561</v>
       </c>
       <c r="H17" s="0">
-        <v>0.11406970359918835</v>
+        <v>0.11661062596676369</v>
       </c>
       <c r="I17" s="0">
-        <v>0.15040637448822844</v>
+        <v>0.17745901225470087</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.82836161602080705</v>
+        <v>0.827379694483243</v>
       </c>
       <c r="B18" s="0">
-        <v>0.534670589878394</v>
+        <v>0.53391786519832096</v>
       </c>
       <c r="C18" s="0">
-        <v>0.83117159222404402</v>
+        <v>0.830127490794629</v>
       </c>
       <c r="D18" s="0">
-        <v>0.76047790423932216</v>
+        <v>0.75743329147030225</v>
       </c>
       <c r="E18" s="0">
-        <v>0.41934458825505844</v>
+        <v>0.41611713605705442</v>
       </c>
       <c r="F18" s="0">
-        <v>0.69085807267951871</v>
+        <v>0.66146255282355348</v>
       </c>
       <c r="G18" s="0">
-        <v>0.065947109832833459</v>
+        <v>0.068510782653327357</v>
       </c>
       <c r="H18" s="0">
-        <v>0.1140328772894786</v>
+        <v>0.11670113998137602</v>
       </c>
       <c r="I18" s="0">
-        <v>0.14051270446839842</v>
+        <v>0.16862778659632655</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.84707504333436301</v>
+        <v>0.84835086481104505</v>
       </c>
       <c r="B19" s="0">
-        <v>0.55565458623846398</v>
+        <v>0.55697233628172305</v>
       </c>
       <c r="C19" s="0">
-        <v>0.83573903477000899</v>
+        <v>0.83771551510034903</v>
       </c>
       <c r="D19" s="0">
-        <v>0.78612237176582977</v>
+        <v>0.7832275661419259</v>
       </c>
       <c r="E19" s="0">
-        <v>0.44383483118913308</v>
+        <v>0.44098196282056151</v>
       </c>
       <c r="F19" s="0">
-        <v>0.71156765602261085</v>
+        <v>0.6836244194417177</v>
       </c>
       <c r="G19" s="0">
-        <v>0.060203702694018132</v>
+        <v>0.063827669997892272</v>
       </c>
       <c r="H19" s="0">
-        <v>0.1130740072328027</v>
+        <v>0.11660626528290098</v>
       </c>
       <c r="I19" s="0">
-        <v>0.12588527988236303</v>
+        <v>0.15588637561858967</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.86851145666905205</v>
+        <v>0.86853860467489397</v>
       </c>
       <c r="B20" s="0">
-        <v>0.583232622339246</v>
+        <v>0.58343858989609199</v>
       </c>
       <c r="C20" s="0">
-        <v>0.85584344397685197</v>
+        <v>0.85914274404847102</v>
       </c>
       <c r="D20" s="0">
-        <v>0.81020204481398428</v>
+        <v>0.80745386165383215</v>
       </c>
       <c r="E20" s="0">
-        <v>0.46831564681119053</v>
+        <v>0.46560517159317122</v>
       </c>
       <c r="F20" s="0">
-        <v>0.73213915217307413</v>
+        <v>0.70558071503160336</v>
       </c>
       <c r="G20" s="0">
-        <v>0.05715025668087674</v>
+        <v>0.060291309970125564</v>
       </c>
       <c r="H20" s="0">
-        <v>0.11482093740233344</v>
+        <v>0.11726502915254884</v>
       </c>
       <c r="I20" s="0">
-        <v>0.12172826817888417</v>
+        <v>0.15045787215067846</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.88617890660978904</v>
+        <v>0.88576831446323501</v>
       </c>
       <c r="B21" s="0">
-        <v>0.60797977728093799</v>
+        <v>0.60363100537955805</v>
       </c>
       <c r="C21" s="0">
-        <v>0.85741581256950195</v>
+        <v>0.85105416081762497</v>
       </c>
       <c r="D21" s="0">
-        <v>0.83324203717485568</v>
+        <v>0.83092566731032436</v>
       </c>
       <c r="E21" s="0">
-        <v>0.49204026723381861</v>
+        <v>0.48927900844111322</v>
       </c>
       <c r="F21" s="0">
-        <v>0.75169256054077482</v>
+        <v>0.72619638205130277</v>
       </c>
       <c r="G21" s="0">
-        <v>0.053654255374288286</v>
+        <v>0.054900016884163898</v>
       </c>
       <c r="H21" s="0">
-        <v>0.11257172332528274</v>
+        <v>0.11310376170407592</v>
       </c>
       <c r="I21" s="0">
-        <v>0.10759255816832905</v>
+        <v>0.128322664444672</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0.90241457649765799</v>
+        <v>0.90158683143204899</v>
       </c>
       <c r="B22" s="0">
-        <v>0.61561888604761394</v>
+        <v>0.61913064457803202</v>
       </c>
       <c r="C22" s="0">
-        <v>0.87478744760976102</v>
+        <v>0.87647748440273199</v>
       </c>
       <c r="D22" s="0">
-        <v>0.85595353771694271</v>
+        <v>0.85335984938719678</v>
       </c>
       <c r="E22" s="0">
-        <v>0.51427445643209924</v>
+        <v>0.5122142848453608</v>
       </c>
       <c r="F22" s="0">
-        <v>0.7708005930445766</v>
+        <v>0.74686171931539747</v>
       </c>
       <c r="G22" s="0">
-        <v>0.04819869809760749</v>
+        <v>0.050712138854266446</v>
       </c>
       <c r="H22" s="0">
-        <v>0.10445768503153954</v>
+        <v>0.10801203201204142</v>
       </c>
       <c r="I22" s="0">
-        <v>0.10316784936246345</v>
+        <v>0.12791607193553431</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.92693953330173195</v>
+        <v>0.92810849978448795</v>
       </c>
       <c r="B23" s="0">
-        <v>0.63908642755561795</v>
+        <v>0.63949922037890705</v>
       </c>
       <c r="C23" s="0">
-        <v>0.887777142744265</v>
+        <v>0.88859165537036799</v>
       </c>
       <c r="D23" s="0">
-        <v>0.87754997158962778</v>
+        <v>0.87532048620442826</v>
       </c>
       <c r="E23" s="0">
-        <v>0.53703613042702547</v>
+        <v>0.53495703579105758</v>
       </c>
       <c r="F23" s="0">
-        <v>0.78930016729291375</v>
+        <v>0.76654859091272221</v>
       </c>
       <c r="G23" s="0">
-        <v>0.046115932771121373</v>
+        <v>0.048985004548184545</v>
       </c>
       <c r="H23" s="0">
-        <v>0.10295898025558167</v>
+        <v>0.10590317952831528</v>
       </c>
       <c r="I23" s="0">
-        <v>0.09828157195162443</v>
+        <v>0.12234028314336623</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.94362439785109598</v>
+        <v>0.94369543774823295</v>
       </c>
       <c r="B24" s="0">
-        <v>0.66491808645777295</v>
+        <v>0.66465944834409996</v>
       </c>
       <c r="C24" s="0">
-        <v>0.89642947469327805</v>
+        <v>0.89968011128637204</v>
       </c>
       <c r="D24" s="0">
-        <v>0.89746080453614241</v>
+        <v>0.89532331740340287</v>
       </c>
       <c r="E24" s="0">
-        <v>0.56004725508126629</v>
+        <v>0.55804091130105182</v>
       </c>
       <c r="F24" s="0">
-        <v>0.80731416600954831</v>
+        <v>0.78584375548690999</v>
       </c>
       <c r="G24" s="0">
-        <v>0.045065794849359471</v>
+        <v>0.047374076493264687</v>
       </c>
       <c r="H24" s="0">
-        <v>0.10403263498030403</v>
+        <v>0.10617988691754857</v>
       </c>
       <c r="I24" s="0">
-        <v>0.088822729917229809</v>
+        <v>0.1126958012009044</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.95832527611253804</v>
+        <v>0.95792494658550498</v>
       </c>
       <c r="B25" s="0">
-        <v>0.68488795181432705</v>
+        <v>0.68504137118673303</v>
       </c>
       <c r="C25" s="0">
-        <v>0.89913474563308105</v>
+        <v>0.89656724988247705</v>
       </c>
       <c r="D25" s="0">
-        <v>0.91644051926723324</v>
+        <v>0.91441356039218935</v>
       </c>
       <c r="E25" s="0">
-        <v>0.58233816572108321</v>
+        <v>0.58047458684570519</v>
       </c>
       <c r="F25" s="0">
-        <v>0.82465779892705149</v>
+        <v>0.80426812763593913</v>
       </c>
       <c r="G25" s="0">
-        <v>0.043157521825629409</v>
+        <v>0.044790816680387181</v>
       </c>
       <c r="H25" s="0">
-        <v>0.10140839210443955</v>
+        <v>0.10320786662175024</v>
       </c>
       <c r="I25" s="0">
-        <v>0.075258885312968399</v>
+        <v>0.09385808681117716</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.97608438361535599</v>
+        <v>0.97527512609380296</v>
       </c>
       <c r="B26" s="0">
-        <v>0.69754031331273902</v>
+        <v>0.697622542074675</v>
       </c>
       <c r="C26" s="0">
-        <v>0.90902019391894495</v>
+        <v>0.90829704515950405</v>
       </c>
       <c r="D26" s="0">
-        <v>0.93494241828567104</v>
+        <v>0.93299868748803305</v>
       </c>
       <c r="E26" s="0">
-        <v>0.60362013002677684</v>
+        <v>0.6018727300613832</v>
       </c>
       <c r="F26" s="0">
-        <v>0.84152257353056181</v>
+        <v>0.82234200828152448</v>
       </c>
       <c r="G26" s="0">
-        <v>0.04012019864204925</v>
+        <v>0.041835255614478775</v>
       </c>
       <c r="H26" s="0">
-        <v>0.094419181249315684</v>
+        <v>0.096164920451135269</v>
       </c>
       <c r="I26" s="0">
-        <v>0.067435868505211161</v>
+        <v>0.085617862909793854</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.98546578061532997</v>
+        <v>0.98650699696856503</v>
       </c>
       <c r="B27" s="0">
-        <v>0.71132172998004695</v>
+        <v>0.71114857043903301</v>
       </c>
       <c r="C27" s="0">
-        <v>0.92012840801707596</v>
+        <v>0.91977185451350896</v>
       </c>
       <c r="D27" s="0">
-        <v>0.95234412457680373</v>
+        <v>0.95064059098438225</v>
       </c>
       <c r="E27" s="0">
-        <v>0.62455856573425994</v>
+        <v>0.62284281594429436</v>
       </c>
       <c r="F27" s="0">
-        <v>0.85794409888765533</v>
+        <v>0.83986932509369461</v>
       </c>
       <c r="G27" s="0">
-        <v>0.03536073686118512</v>
+        <v>0.037385514258850207</v>
       </c>
       <c r="H27" s="0">
-        <v>0.086489184312718029</v>
+        <v>0.088046026052493495</v>
       </c>
       <c r="I27" s="0">
-        <v>0.061715274683970603</v>
+        <v>0.079786629415700847</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>1.00149134972281</v>
+        <v>1.00175821906179</v>
       </c>
       <c r="B28" s="0">
-        <v>0.72431440242374001</v>
+        <v>0.72380786049684398</v>
       </c>
       <c r="C28" s="0">
-        <v>0.92733820908195597</v>
+        <v>0.93013274115228395</v>
       </c>
       <c r="D28" s="0">
-        <v>0.96956872426394825</v>
+        <v>0.96792064674747091</v>
       </c>
       <c r="E28" s="0">
-        <v>0.64492845677396948</v>
+        <v>0.64330847512535849</v>
       </c>
       <c r="F28" s="0">
-        <v>0.87370730042325229</v>
+        <v>0.85679469158162203</v>
       </c>
       <c r="G28" s="0">
-        <v>0.030676942854647195</v>
+        <v>0.032408601797655763</v>
       </c>
       <c r="H28" s="0">
-        <v>0.078856902083212846</v>
+        <v>0.080409604577036983</v>
       </c>
       <c r="I28" s="0">
-        <v>0.054356880532646472</v>
+        <v>0.073156704918715856</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>1.01195812225805</v>
+        <v>1.0113721758410601</v>
       </c>
       <c r="B29" s="0">
-        <v>0.73447829537532605</v>
+        <v>0.73539796886228304</v>
       </c>
       <c r="C29" s="0">
-        <v>0.94064147740926696</v>
+        <v>0.93789433781645304</v>
       </c>
       <c r="D29" s="0">
-        <v>0.98596185805945402</v>
+        <v>0.98432307700457045</v>
       </c>
       <c r="E29" s="0">
-        <v>0.64923880390917754</v>
+        <v>0.64779303860635407</v>
       </c>
       <c r="F29" s="0">
-        <v>0.88919327509348356</v>
+        <v>0.87324169110871663</v>
       </c>
       <c r="G29" s="0">
-        <v>0.025773093961159139</v>
+        <v>0.027111914461356072</v>
       </c>
       <c r="H29" s="0">
-        <v>0.073730517243810259</v>
+        <v>0.075519543578497272</v>
       </c>
       <c r="I29" s="0">
-        <v>0.049717931859550542</v>
+        <v>0.064044812508335158</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>1.02783911433288</v>
+        <v>1.0272536023873799</v>
       </c>
       <c r="B30" s="0">
-        <v>0.75049057488013005</v>
+        <v>0.75047801562365901</v>
       </c>
       <c r="C30" s="0">
-        <v>0.94094463457307298</v>
+        <v>0.94257607140323096</v>
       </c>
       <c r="D30" s="0">
-        <v>1.0009508569792755</v>
+        <v>0.99937892082195279</v>
       </c>
       <c r="E30" s="0">
-        <v>0.67033076115624313</v>
+        <v>0.66890349395795512</v>
       </c>
       <c r="F30" s="0">
-        <v>0.90419815667964742</v>
+        <v>0.88937003403394832</v>
       </c>
       <c r="G30" s="0">
-        <v>0.025494605663317554</v>
+        <v>0.027057772306382448</v>
       </c>
       <c r="H30" s="0">
-        <v>0.075556528232216216</v>
+        <v>0.077136151756734203</v>
       </c>
       <c r="I30" s="0">
-        <v>0.039182282750240383</v>
+        <v>0.054685490027646402</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>1.0368415987864901</v>
+        <v>1.0376215554222501</v>
       </c>
       <c r="B31" s="0">
-        <v>0.75757173931875399</v>
+        <v>0.75705034716028496</v>
       </c>
       <c r="C31" s="0">
-        <v>0.95890076570203797</v>
+        <v>0.95676910401260495</v>
       </c>
       <c r="D31" s="0">
-        <v>1.0157328493776681</v>
+        <v>1.0143953368118988</v>
       </c>
       <c r="E31" s="0">
-        <v>0.68966338804244143</v>
+        <v>0.68819515954095145</v>
       </c>
       <c r="F31" s="0">
-        <v>0.91908103244198791</v>
+        <v>0.9051361771324743</v>
       </c>
       <c r="G31" s="0">
-        <v>0.021759200828390234</v>
+        <v>0.023442751099227326</v>
       </c>
       <c r="H31" s="0">
-        <v>0.068579981656019126</v>
+        <v>0.069514188802438537</v>
       </c>
       <c r="I31" s="0">
-        <v>0.038638818450550803</v>
+        <v>0.051315235305949877</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>1.0440211686665699</v>
+        <v>1.04445076473676</v>
       </c>
       <c r="B32" s="0">
-        <v>0.76626484086761903</v>
+        <v>0.76561247716353797</v>
       </c>
       <c r="C32" s="0">
-        <v>0.96342953767239203</v>
+        <v>0.96538938358182003</v>
       </c>
       <c r="D32" s="0">
-        <v>1.0300011466760972</v>
+        <v>1.0287273762269424</v>
       </c>
       <c r="E32" s="0">
-        <v>0.7083562184941834</v>
+        <v>0.70692026079768966</v>
       </c>
       <c r="F32" s="0">
-        <v>0.93334353630619682</v>
+        <v>0.92044276599069208</v>
       </c>
       <c r="G32" s="0">
-        <v>0.014827980462210228</v>
+        <v>0.01625828455710876</v>
       </c>
       <c r="H32" s="0">
-        <v>0.058837681756804427</v>
+        <v>0.059455174608219086</v>
       </c>
       <c r="I32" s="0">
-        <v>0.029599024419904672</v>
+        <v>0.043451893237943004</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>1.0524569044149901</v>
+        <v>1.0518522433564701</v>
       </c>
       <c r="B33" s="0">
-        <v>0.777085695540782</v>
+        <v>0.77489739144743297</v>
       </c>
       <c r="C33" s="0">
-        <v>0.96049511999317705</v>
+        <v>0.95754082785598504</v>
       </c>
       <c r="D33" s="0">
-        <v>1.0437755790669327</v>
+        <v>1.0426546867404254</v>
       </c>
       <c r="E33" s="0">
-        <v>0.72674203337382237</v>
+        <v>0.72531267828799306</v>
       </c>
       <c r="F33" s="0">
-        <v>0.94717802445603017</v>
+        <v>0.93507815707678432</v>
       </c>
       <c r="G33" s="0">
-        <v>0.0086397257357799847</v>
+        <v>0.0090249488516898242</v>
       </c>
       <c r="H33" s="0">
-        <v>0.049791933229814254</v>
+        <v>0.050187065362251343</v>
       </c>
       <c r="I33" s="0">
-        <v>0.013551819712016017</v>
+        <v>0.024010182123704583</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>1.06107673537104</v>
+        <v>1.06050417832581</v>
       </c>
       <c r="B34" s="0">
-        <v>0.78372897185146695</v>
+        <v>0.787134626290932</v>
       </c>
       <c r="C34" s="0">
-        <v>0.95948814870750498</v>
+        <v>0.96397810546922602</v>
       </c>
       <c r="D34" s="0">
-        <v>1.0572014658643458</v>
+        <v>1.0558345910872371</v>
       </c>
       <c r="E34" s="0">
-        <v>0.74451861942416198</v>
+        <v>0.74349858354293374</v>
       </c>
       <c r="F34" s="0">
-        <v>0.9607514573850191</v>
+        <v>0.94977853121468581</v>
       </c>
       <c r="G34" s="0">
-        <v>0.0040304812793836905</v>
+        <v>0.0055695089114114549</v>
       </c>
       <c r="H34" s="0">
-        <v>0.039886339473560642</v>
+        <v>0.042699869541468247</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.0010695269983628686</v>
+        <v>0.01280966385841267</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>1.07260169064198</v>
+        <v>1.07330410620738</v>
       </c>
       <c r="B35" s="0">
-        <v>0.79317827705269695</v>
+        <v>0.792690515791031</v>
       </c>
       <c r="C35" s="0">
-        <v>0.96512889230300003</v>
+        <v>0.96111978862079706</v>
       </c>
       <c r="D35" s="0">
-        <v>1.0701104766491643</v>
+        <v>1.0691169289230245</v>
       </c>
       <c r="E35" s="0">
-        <v>0.761961319112197</v>
+        <v>0.76071260675781016</v>
       </c>
       <c r="F35" s="0">
-        <v>0.97419319506565227</v>
+        <v>0.96384140705753696</v>
       </c>
       <c r="G35" s="0">
-        <v>0.0019587469709926629</v>
+        <v>0.0032212781518725512</v>
       </c>
       <c r="H35" s="0">
-        <v>0.030209515974069599</v>
+        <v>0.031555484159521738</v>
       </c>
       <c r="I35" s="0">
-        <v>-0.0088779215726923124</v>
+        <v>-0.001155161395229039</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>1.0804360459297</v>
+        <v>1.0809203013276301</v>
       </c>
       <c r="B36" s="0">
-        <v>0.79679592658466003</v>
+        <v>0.79596459231362404</v>
       </c>
       <c r="C36" s="0">
-        <v>0.97657515624084701</v>
+        <v>0.97782287290922199</v>
       </c>
       <c r="D36" s="0">
-        <v>1.0827679587814572</v>
+        <v>1.0817980083657501</v>
       </c>
       <c r="E36" s="0">
-        <v>0.77862223662234276</v>
+        <v>0.77737706688774633</v>
       </c>
       <c r="F36" s="0">
-        <v>0.98744948798434218</v>
+        <v>0.97804145220923233</v>
       </c>
       <c r="G36" s="0">
-        <v>-0.00023852484270606107</v>
+        <v>0.00079842527173803297</v>
       </c>
       <c r="H36" s="0">
-        <v>0.01792299100334014</v>
+        <v>0.018922437736809978</v>
       </c>
       <c r="I36" s="0">
-        <v>-0.009959704782667906</v>
+        <v>2.3505641842673976e-05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>1.09323525567388</v>
+        <v>1.0925220894949299</v>
       </c>
       <c r="B37" s="0">
-        <v>0.79997261408051801</v>
+        <v>0.80148793446295197</v>
       </c>
       <c r="C37" s="0">
-        <v>0.99728643526952399</v>
+        <v>0.99834945377080597</v>
       </c>
       <c r="D37" s="0">
-        <v>1.0955110937665347</v>
+        <v>1.09443264802799</v>
       </c>
       <c r="E37" s="0">
-        <v>0.79473286781006125</v>
+        <v>0.79366669386718025</v>
       </c>
       <c r="F37" s="0">
-        <v>1.0006237293941942</v>
+        <v>0.99204705687919448</v>
       </c>
       <c r="G37" s="0">
-        <v>-0.0020937257439658501</v>
+        <v>-0.0011274421626428722</v>
       </c>
       <c r="H37" s="0">
-        <v>0.0056541420079637356</v>
+        <v>0.0073759466994909239</v>
       </c>
       <c r="I37" s="0">
-        <v>-0.0055097353069919613</v>
+        <v>0.0046134755394729452</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>1.1026428181724099</v>
+        <v>1.10236930410228</v>
       </c>
       <c r="B38" s="0">
-        <v>0.80496267587022197</v>
+        <v>0.80463350526609401</v>
       </c>
       <c r="C38" s="0">
-        <v>0.99625516279152304</v>
+        <v>0.99943280943192103</v>
       </c>
       <c r="D38" s="0">
-        <v>1.1081979666192154</v>
+        <v>1.1072498105069701</v>
       </c>
       <c r="E38" s="0">
-        <v>0.81064392549087949</v>
+        <v>0.80949216511944244</v>
       </c>
       <c r="F38" s="0">
-        <v>1.0131507542273155</v>
+        <v>1.005383857948315</v>
       </c>
       <c r="G38" s="0">
-        <v>-0.0061883072589567463</v>
+        <v>-0.0052644774531635926</v>
       </c>
       <c r="H38" s="0">
-        <v>-0.0059084095217750562</v>
+        <v>-0.0045981017455692698</v>
       </c>
       <c r="I38" s="0">
-        <v>-0.015747781966183306</v>
+        <v>-0.006050569362789312</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>1.1087649574821199</v>
+        <v>1.1091753208036099</v>
       </c>
       <c r="B39" s="0">
-        <v>0.81189298183172098</v>
+        <v>0.81163218469012299</v>
       </c>
       <c r="C39" s="0">
-        <v>1.00576374018327</v>
+        <v>0.999746060076804</v>
       </c>
       <c r="D39" s="0">
-        <v>1.1205492248957851</v>
+        <v>1.1197971925630927</v>
       </c>
       <c r="E39" s="0">
-        <v>0.8265843858472719</v>
+        <v>0.82539983227125457</v>
       </c>
       <c r="F39" s="0">
-        <v>1.0257883599290409</v>
+        <v>1.018555322220585</v>
       </c>
       <c r="G39" s="0">
-        <v>-0.010851518650915713</v>
+        <v>-0.010159337692705991</v>
       </c>
       <c r="H39" s="0">
-        <v>-0.013549729008053334</v>
+        <v>-0.012878491382627109</v>
       </c>
       <c r="I39" s="0">
-        <v>-0.020164493818509408</v>
+        <v>-0.017382291917517032</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>1.12143377843153</v>
+        <v>1.1219047929549999</v>
       </c>
       <c r="B40" s="0">
-        <v>0.82844008349203402</v>
+        <v>0.82749014342418103</v>
       </c>
       <c r="C40" s="0">
-        <v>1.0184190941670399</v>
+        <v>1.0191387815309501</v>
       </c>
       <c r="D40" s="0">
-        <v>1.1327546755930293</v>
+        <v>1.1320139604204182</v>
       </c>
       <c r="E40" s="0">
-        <v>0.84285022019878486</v>
+        <v>0.84169941219922739</v>
       </c>
       <c r="F40" s="0">
-        <v>1.0383603551030722</v>
+        <v>1.0319887281496212</v>
       </c>
       <c r="G40" s="0">
-        <v>-0.012678855578687602</v>
+        <v>-0.011907054811189911</v>
       </c>
       <c r="H40" s="0">
-        <v>-0.014141166479219253</v>
+        <v>-0.01335041530878766</v>
       </c>
       <c r="I40" s="0">
-        <v>-0.020028752320244196</v>
+        <v>-0.013806723083075519</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>1.1310396710028201</v>
+        <v>1.13048624057531</v>
       </c>
       <c r="B41" s="0">
-        <v>0.85019629164875699</v>
+        <v>0.85170505735479096</v>
       </c>
       <c r="C41" s="0">
-        <v>1.0329102018479499</v>
+        <v>1.03357530574426</v>
       </c>
       <c r="D41" s="0">
-        <v>1.1445178683134536</v>
+        <v>1.1436648379354983</v>
       </c>
       <c r="E41" s="0">
-        <v>0.85913580458934169</v>
+        <v>0.85816019488001349</v>
       </c>
       <c r="F41" s="0">
-        <v>1.0508943633032695</v>
+        <v>1.0452362668081068</v>
       </c>
       <c r="G41" s="0">
-        <v>-0.012943473715864936</v>
+        <v>-0.012122830670641743</v>
       </c>
       <c r="H41" s="0">
-        <v>-0.01138164029560205</v>
+        <v>-0.0097625347330666298</v>
       </c>
       <c r="I41" s="0">
-        <v>-0.017158763247964275</v>
+        <v>-0.010015442749579993</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>1.1440151457494101</v>
+        <v>1.14379045860706</v>
       </c>
       <c r="B42" s="0">
-        <v>0.861331955435095</v>
+        <v>0.86093809120014297</v>
       </c>
       <c r="C42" s="0">
-        <v>1.05426890193111</v>
+        <v>1.0597688325140899</v>
       </c>
       <c r="D42" s="0">
-        <v>1.1566810197829638</v>
+        <v>1.1559030547782017</v>
       </c>
       <c r="E42" s="0">
-        <v>0.87454874034010088</v>
+        <v>0.87349303185325433</v>
       </c>
       <c r="F42" s="0">
-        <v>1.0633410528123088</v>
+        <v>1.0584453241281224</v>
       </c>
       <c r="G42" s="0">
-        <v>-0.013033579269491705</v>
+        <v>-0.012155296947854241</v>
       </c>
       <c r="H42" s="0">
-        <v>-0.0093259784828422718</v>
+        <v>-0.0079762103897394986</v>
       </c>
       <c r="I42" s="0">
-        <v>-0.010743862469263342</v>
+        <v>-0.00223421256344468</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>1.15874132874604</v>
+        <v>1.1589865859124899</v>
       </c>
       <c r="B43" s="0">
-        <v>0.89298177137311496</v>
+        <v>0.89305403518066395</v>
       </c>
       <c r="C43" s="0">
-        <v>1.0637266559294301</v>
+        <v>1.0563781615124399</v>
       </c>
       <c r="D43" s="0">
-        <v>1.1680013277686647</v>
+        <v>1.1673968174214855</v>
       </c>
       <c r="E43" s="0">
-        <v>0.89071056160010587</v>
+        <v>0.88963228661450389</v>
       </c>
       <c r="F43" s="0">
-        <v>1.0756167405982677</v>
+        <v>1.0710763640834193</v>
       </c>
       <c r="G43" s="0">
-        <v>-0.0084952802591706129</v>
+        <v>-0.0078356768787546608</v>
       </c>
       <c r="H43" s="0">
-        <v>-0.0014418588948812425</v>
+        <v>-0.00086768237394106544</v>
       </c>
       <c r="I43" s="0">
-        <v>-0.010729053858692671</v>
+        <v>-0.011418680510858179</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>1.1761475795774401</v>
+        <v>1.17658219728986</v>
       </c>
       <c r="B44" s="0">
-        <v>0.90484269910362203</v>
+        <v>0.90360189138594504</v>
       </c>
       <c r="C44" s="0">
-        <v>1.0840318835437099</v>
+        <v>1.0846455591037401</v>
       </c>
       <c r="D44" s="0">
-        <v>1.1800102694749279</v>
+        <v>1.1794600991180815</v>
       </c>
       <c r="E44" s="0">
-        <v>0.90545213610092556</v>
+        <v>0.90431946002490493</v>
       </c>
       <c r="F44" s="0">
-        <v>1.0878400638928249</v>
+        <v>1.0840743790299663</v>
       </c>
       <c r="G44" s="0">
-        <v>-0.0036388283778748167</v>
+        <v>-0.0029630572416367547</v>
       </c>
       <c r="H44" s="0">
-        <v>0.00070659983910268873</v>
+        <v>0.00072263277700484042</v>
       </c>
       <c r="I44" s="0">
-        <v>-0.0031835981296686614</v>
+        <v>0.00011719959274556506</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>1.19276187863284</v>
+        <v>1.1923911942699399</v>
       </c>
       <c r="B45" s="0">
-        <v>0.92424534057382102</v>
+        <v>0.92225145092462602</v>
       </c>
       <c r="C45" s="0">
-        <v>1.1132811632956701</v>
+        <v>1.11361528586492</v>
       </c>
       <c r="D45" s="0">
-        <v>1.1916192225573317</v>
+        <v>1.191159324365741</v>
       </c>
       <c r="E45" s="0">
-        <v>0.92017410722126569</v>
+        <v>0.9190452003738514</v>
       </c>
       <c r="F45" s="0">
-        <v>1.1002483234109264</v>
+        <v>1.0970424206413845</v>
       </c>
       <c r="G45" s="0">
-        <v>0.0015233340008804289</v>
+        <v>0.001489308218426789</v>
       </c>
       <c r="H45" s="0">
-        <v>0.0035428777454808123</v>
+        <v>0.0036990873394107796</v>
       </c>
       <c r="I45" s="0">
-        <v>0.0122445552912474</v>
+        <v>0.016642851374441003</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>1.2076672394343</v>
+        <v>1.20744183060729</v>
       </c>
       <c r="B46" s="0">
-        <v>0.938895011958083</v>
+        <v>0.94193766982180804</v>
       </c>
       <c r="C46" s="0">
-        <v>1.1321805285965201</v>
+        <v>1.1386763600651799</v>
       </c>
       <c r="D46" s="0">
-        <v>1.2034206303060464</v>
+        <v>1.2027249544121628</v>
       </c>
       <c r="E46" s="0">
-        <v>0.93448647926758022</v>
+        <v>0.93372669921364526</v>
       </c>
       <c r="F46" s="0">
-        <v>1.1123694978919312</v>
+        <v>1.1099270055827228</v>
       </c>
       <c r="G46" s="0">
-        <v>0.0046968560233249246</v>
+        <v>0.005591827292965772</v>
       </c>
       <c r="H46" s="0">
-        <v>0.0051749732496608712</v>
+        <v>0.0077585333873263435</v>
       </c>
       <c r="I46" s="0">
-        <v>0.019478376298015843</v>
+        <v>0.026456441810784315</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>1.2226997211803099</v>
+        <v>1.2227618696532001</v>
       </c>
       <c r="B47" s="0">
-        <v>0.95647430723752402</v>
+        <v>0.95680674616073802</v>
       </c>
       <c r="C47" s="0">
-        <v>1.1422471916313199</v>
+        <v>1.13472818959376</v>
       </c>
       <c r="D47" s="0">
-        <v>1.2151231414500387</v>
+        <v>1.21470211728931</v>
       </c>
       <c r="E47" s="0">
-        <v>0.94883619332326508</v>
+        <v>0.94791695947052801</v>
       </c>
       <c r="F47" s="0">
-        <v>1.1243689843323459</v>
+        <v>1.1221362995754125</v>
       </c>
       <c r="G47" s="0">
-        <v>0.0066709591965062017</v>
+        <v>0.0071188826587831053</v>
       </c>
       <c r="H47" s="0">
-        <v>0.0075841194578649702</v>
+        <v>0.0088247671410240838</v>
       </c>
       <c r="I47" s="0">
-        <v>0.01869368556598059</v>
+        <v>0.015589853640277021</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>1.23279177526299</v>
+        <v>1.2332178782123699</v>
       </c>
       <c r="B48" s="0">
-        <v>0.97282688006693196</v>
+        <v>0.97144262441773699</v>
       </c>
       <c r="C48" s="0">
-        <v>1.1529520027853699</v>
+        <v>1.1533949649822699</v>
       </c>
       <c r="D48" s="0">
-        <v>1.2265152540072659</v>
+        <v>1.2261480719310158</v>
       </c>
       <c r="E48" s="0">
-        <v>0.96310400848351674</v>
+        <v>0.96210180966208991</v>
       </c>
       <c r="F48" s="0">
-        <v>1.1364825991528873</v>
+        <v>1.1349289800660847</v>
       </c>
       <c r="G48" s="0">
-        <v>0.0064092998348864181</v>
+        <v>0.006844534398377157</v>
       </c>
       <c r="H48" s="0">
-        <v>0.0093970474698279981</v>
+        <v>0.0099508900887637485</v>
       </c>
       <c r="I48" s="0">
-        <v>0.014544904663965918</v>
+        <v>0.015682124772016408</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>1.2425541233058699</v>
+        <v>1.2424659049367399</v>
       </c>
       <c r="B49" s="0">
-        <v>0.98487165017469003</v>
+        <v>0.98642807114986397</v>
       </c>
       <c r="C49" s="0">
-        <v>1.14262456023226</v>
+        <v>1.14505191146661</v>
       </c>
       <c r="D49" s="0">
-        <v>1.238131130871287</v>
+        <v>1.2376477218220696</v>
       </c>
       <c r="E49" s="0">
-        <v>0.97697504626733811</v>
+        <v>0.97615305990184043</v>
       </c>
       <c r="F49" s="0">
-        <v>1.1481095796273317</v>
+        <v>1.1471212119077816</v>
       </c>
       <c r="G49" s="0">
-        <v>0.003119054664993771</v>
+        <v>0.0037352368541160976</v>
       </c>
       <c r="H49" s="0">
-        <v>0.0087530206233962619</v>
+        <v>0.010185077827627917</v>
       </c>
       <c r="I49" s="0">
-        <v>-0.0029897428583356362</v>
+        <v>0.00070902415478313124</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>1.24995526544962</v>
+        <v>1.2495726418141899</v>
       </c>
       <c r="B50" s="0">
-        <v>1.0008196247458001</v>
+        <v>1.0002676172599501</v>
       </c>
       <c r="C50" s="0">
-        <v>1.15644687673923</v>
+        <v>1.1605040721758799</v>
       </c>
       <c r="D50" s="0">
-        <v>1.2490218767818342</v>
+        <v>1.2486263776352058</v>
       </c>
       <c r="E50" s="0">
-        <v>0.99101988136178243</v>
+        <v>0.99011901502801192</v>
       </c>
       <c r="F50" s="0">
-        <v>1.1603695662724978</v>
+        <v>1.1598856014279135</v>
       </c>
       <c r="G50" s="0">
-        <v>0.00040679476605751287</v>
+        <v>0.00070222428630386223</v>
       </c>
       <c r="H50" s="0">
-        <v>0.0094919675275516851</v>
+        <v>0.010513390095143689</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.0056505083686385739</v>
+        <v>-0.0024196737614336026</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>1.2552293745010901</v>
+        <v>1.2551501178055</v>
       </c>
       <c r="B51" s="0">
-        <v>1.0124802299119899</v>
+        <v>1.0127823864288801</v>
       </c>
       <c r="C51" s="0">
-        <v>1.15655147171253</v>
+        <v>1.14980909846474</v>
       </c>
       <c r="D51" s="0">
-        <v>1.2599952232975027</v>
+        <v>1.2597279904187546</v>
       </c>
       <c r="E51" s="0">
-        <v>1.0045112901235413</v>
+        <v>1.0036324429840187</v>
       </c>
       <c r="F51" s="0">
-        <v>1.1722735252927259</v>
+        <v>1.1720180603544519</v>
       </c>
       <c r="G51" s="0">
-        <v>-0.0028930639120054937</v>
+        <v>-0.0028542726766888626</v>
       </c>
       <c r="H51" s="0">
-        <v>0.0066829030521968818</v>
+        <v>0.007277824888714265</v>
       </c>
       <c r="I51" s="0">
-        <v>-0.014725075493365707</v>
+        <v>-0.019416051894573284</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>1.2656873231713599</v>
+        <v>1.2661692062214001</v>
       </c>
       <c r="B52" s="0">
-        <v>1.01689886099728</v>
+        <v>1.01566801549639</v>
       </c>
       <c r="C52" s="0">
-        <v>1.16765300112967</v>
+        <v>1.1681295201759001</v>
       </c>
       <c r="D52" s="0">
-        <v>1.271476347630782</v>
+        <v>1.2712656245187595</v>
       </c>
       <c r="E52" s="0">
-        <v>1.0171550036820878</v>
+        <v>1.0162620853722395</v>
       </c>
       <c r="F52" s="0">
-        <v>1.184277660065802</v>
+        <v>1.1846080364302831</v>
       </c>
       <c r="G52" s="0">
-        <v>-0.0055378477111412468</v>
+        <v>-0.0052098094032432879</v>
       </c>
       <c r="H52" s="0">
-        <v>-0.00041935385106141602</v>
+        <v>8.9472643308916879e-05</v>
       </c>
       <c r="I52" s="0">
-        <v>-0.016279456295512182</v>
+        <v>-0.017118528904088399</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>1.27400736915698</v>
+        <v>1.27419383430037</v>
       </c>
       <c r="B53" s="0">
-        <v>1.0197501047233299</v>
+        <v>1.0214128231825299</v>
       </c>
       <c r="C53" s="0">
-        <v>1.18343143565967</v>
+        <v>1.1838665578566701</v>
       </c>
       <c r="D53" s="0">
-        <v>1.2830511092687058</v>
+        <v>1.2827475955382828</v>
       </c>
       <c r="E53" s="0">
-        <v>1.0295775600972126</v>
+        <v>1.0288728148158786</v>
       </c>
       <c r="F53" s="0">
-        <v>1.1963786951305635</v>
+        <v>1.1971473168362654</v>
       </c>
       <c r="G53" s="0">
-        <v>-0.0083714220212789767</v>
+        <v>-0.0078129004467346851</v>
       </c>
       <c r="H53" s="0">
-        <v>-0.0085600534967425097</v>
+        <v>-0.0072596543310343726</v>
       </c>
       <c r="I53" s="0">
-        <v>-0.014072380515777675</v>
+        <v>-0.013626193569016025</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>1.2842411928303099</v>
+        <v>1.2836393399338799</v>
       </c>
       <c r="B54" s="0">
-        <v>1.0283897802059501</v>
+        <v>1.0274844897212101</v>
       </c>
       <c r="C54" s="0">
-        <v>1.18824939762268</v>
+        <v>1.1932774222058899</v>
       </c>
       <c r="D54" s="0">
-        <v>1.2946998171807622</v>
+        <v>1.2944519128847567</v>
       </c>
       <c r="E54" s="0">
-        <v>1.0423526698350207</v>
+        <v>1.041559220793786</v>
       </c>
       <c r="F54" s="0">
-        <v>1.2083203517771013</v>
+        <v>1.2095792937497287</v>
       </c>
       <c r="G54" s="0">
-        <v>-0.010209346790529114</v>
+        <v>-0.010102967799901403</v>
       </c>
       <c r="H54" s="0">
-        <v>-0.014411277343838994</v>
+        <v>-0.01367927378800559</v>
       </c>
       <c r="I54" s="0">
-        <v>-0.019490086686733243</v>
+        <v>-0.017322176818063358</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>1.29579087197946</v>
+        <v>1.29557048678882</v>
       </c>
       <c r="B55" s="0">
-        <v>1.0351915074387901</v>
+        <v>1.03545442887398</v>
       </c>
       <c r="C55" s="0">
-        <v>1.1947485221960601</v>
+        <v>1.18941046652371</v>
       </c>
       <c r="D55" s="0">
-        <v>1.3065391731554998</v>
+        <v>1.3064166434546771</v>
       </c>
       <c r="E55" s="0">
-        <v>1.0551902463663096</v>
+        <v>1.0544397462982587</v>
       </c>
       <c r="F55" s="0">
-        <v>1.2203693617321469</v>
+        <v>1.2217871707066872</v>
       </c>
       <c r="G55" s="0">
-        <v>-0.012078424139592222</v>
+        <v>-0.012273617304040531</v>
       </c>
       <c r="H55" s="0">
-        <v>-0.019669941073861136</v>
+        <v>-0.019190851108465235</v>
       </c>
       <c r="I55" s="0">
-        <v>-0.025768920209744278</v>
+        <v>-0.03092436486001935</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>1.3037542384324301</v>
+        <v>1.3043196511098401</v>
       </c>
       <c r="B56" s="0">
-        <v>1.0434620309920499</v>
+        <v>1.0426006657911999</v>
       </c>
       <c r="C56" s="0">
-        <v>1.1965029348954099</v>
+        <v>1.1965487398485299</v>
       </c>
       <c r="D56" s="0">
-        <v>1.3181609514837251</v>
+        <v>1.3181115006577155</v>
       </c>
       <c r="E56" s="0">
-        <v>1.068339096478865</v>
+        <v>1.0676018496935271</v>
       </c>
       <c r="F56" s="0">
-        <v>1.2324716694997211</v>
+        <v>1.2343644015489159</v>
       </c>
       <c r="G56" s="0">
-        <v>-0.015421217744232751</v>
+        <v>-0.015182072603169006</v>
       </c>
       <c r="H56" s="0">
-        <v>-0.023997552883838057</v>
+        <v>-0.023442806365041449</v>
       </c>
       <c r="I56" s="0">
-        <v>-0.036307815107582554</v>
+        <v>-0.03855536071967422</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>1.3103414910514599</v>
+        <v>1.3108483884025499</v>
       </c>
       <c r="B57" s="0">
-        <v>1.0546188780200001</v>
+        <v>1.05640426438479</v>
       </c>
       <c r="C57" s="0">
-        <v>1.1934396633306401</v>
+        <v>1.19630301259842</v>
       </c>
       <c r="D57" s="0">
-        <v>1.3295148055961921</v>
+        <v>1.3293605084305489</v>
       </c>
       <c r="E57" s="0">
-        <v>1.0818168644079322</v>
+        <v>1.0812681983006505</v>
       </c>
       <c r="F57" s="0">
-        <v>1.2446181158254028</v>
+        <v>1.2469494734035385</v>
       </c>
       <c r="G57" s="0">
-        <v>-0.018657155103680191</v>
+        <v>-0.018026651966673805</v>
       </c>
       <c r="H57" s="0">
-        <v>-0.027495757400839212</v>
+        <v>-0.026180886076240972</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.051559174694359666</v>
+        <v>-0.051213347640391579</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>1.3185500406281601</v>
+        <v>1.3177034888255501</v>
       </c>
       <c r="B58" s="0">
-        <v>1.0639473994184301</v>
+        <v>1.0626264638479901</v>
       </c>
       <c r="C58" s="0">
-        <v>1.1885737759261701</v>
+        <v>1.1901473721096301</v>
       </c>
       <c r="D58" s="0">
-        <v>1.3411243288245833</v>
+        <v>1.3410788155602369</v>
       </c>
       <c r="E58" s="0">
-        <v>1.0949474656739324</v>
+        <v>1.0942792702800039</v>
       </c>
       <c r="F58" s="0">
-        <v>1.2567251686634924</v>
+        <v>1.2593487181133602</v>
       </c>
       <c r="G58" s="0">
-        <v>-0.021575910098987301</v>
+        <v>-0.021905130620486053</v>
       </c>
       <c r="H58" s="0">
-        <v>-0.034338897406033152</v>
+        <v>-0.034152284073502223</v>
       </c>
       <c r="I58" s="0">
-        <v>-0.066055851041099886</v>
+        <v>-0.067562177750873004</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>1.3255662713232199</v>
+        <v>1.3251230822890101</v>
       </c>
       <c r="B59" s="0">
-        <v>1.0575024458584501</v>
+        <v>1.0574981674735699</v>
       </c>
       <c r="C59" s="0">
-        <v>1.2048108240708</v>
+        <v>1.20105475784988</v>
       </c>
       <c r="D59" s="0">
-        <v>1.3535138632591452</v>
+        <v>1.3535436212464051</v>
       </c>
       <c r="E59" s="0">
-        <v>1.1070548806257596</v>
+        <v>1.106475568952997</v>
       </c>
       <c r="F59" s="0">
-        <v>1.2691437890746033</v>
+        <v>1.2719824103084738</v>
       </c>
       <c r="G59" s="0">
-        <v>-0.026650175563806413</v>
+        <v>-0.02713636687443258</v>
       </c>
       <c r="H59" s="0">
-        <v>-0.04651525281697224</v>
+        <v>-0.04626252736878686</v>
       </c>
       <c r="I59" s="0">
-        <v>-0.065577837538279213</v>
+        <v>-0.071354044234937117</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>1.33579811152603</v>
+        <v>1.3365479688962301</v>
       </c>
       <c r="B60" s="0">
-        <v>1.06764621794045</v>
+        <v>1.06734379395318</v>
       </c>
       <c r="C60" s="0">
-        <v>1.2128297732211699</v>
+        <v>1.21245176710019</v>
       </c>
       <c r="D60" s="0">
-        <v>1.3658105154728364</v>
+        <v>1.3659139664835318</v>
       </c>
       <c r="E60" s="0">
-        <v>1.1201225822050329</v>
+        <v>1.1196266999374993</v>
       </c>
       <c r="F60" s="0">
-        <v>1.281523304756611</v>
+        <v>1.2847372762283717</v>
       </c>
       <c r="G60" s="0">
-        <v>-0.029310543032393884</v>
+        <v>-0.029130683940570605</v>
       </c>
       <c r="H60" s="0">
-        <v>-0.052646631653991291</v>
+        <v>-0.051938113453915129</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.070443713975025204</v>
+        <v>-0.07442685545548812</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>1.3491195058371299</v>
+        <v>1.34990358106466</v>
       </c>
       <c r="B61" s="0">
-        <v>1.07653417188213</v>
+        <v>1.0786838811293</v>
       </c>
       <c r="C61" s="0">
-        <v>1.2044792908599</v>
+        <v>1.20491218206137</v>
       </c>
       <c r="D61" s="0">
-        <v>1.3786356175604604</v>
+        <v>1.378644226528942</v>
       </c>
       <c r="E61" s="0">
-        <v>1.1334296392855703</v>
+        <v>1.1331277398112272</v>
       </c>
       <c r="F61" s="0">
-        <v>1.2935662860352335</v>
+        <v>1.297113257079255</v>
       </c>
       <c r="G61" s="0">
-        <v>-0.030343482674363424</v>
+        <v>-0.029734689581772434</v>
       </c>
       <c r="H61" s="0">
-        <v>-0.057182334232446792</v>
+        <v>-0.056007093505976845</v>
       </c>
       <c r="I61" s="0">
-        <v>-0.085901819632972887</v>
+        <v>-0.088630774063375189</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.36130301119526</v>
+        <v>1.36018998034827</v>
       </c>
       <c r="B62" s="0">
-        <v>1.0875026348836401</v>
+        <v>1.0853972029047301</v>
       </c>
       <c r="C62" s="0">
-        <v>1.22585874331316</v>
+        <v>1.22871593286132</v>
       </c>
       <c r="D62" s="0">
-        <v>1.3911798100936856</v>
+        <v>1.3912785020828067</v>
       </c>
       <c r="E62" s="0">
-        <v>1.1471485356615827</v>
+        <v>1.1466816419066843</v>
       </c>
       <c r="F62" s="0">
-        <v>1.3063877044299639</v>
+        <v>1.3102437604352946</v>
       </c>
       <c r="G62" s="0">
-        <v>-0.030656191498431334</v>
+        <v>-0.03118693015979546</v>
       </c>
       <c r="H62" s="0">
-        <v>-0.059647799295312345</v>
+        <v>-0.060064871496717839</v>
       </c>
       <c r="I62" s="0">
-        <v>-0.082562483099971981</v>
+        <v>-0.084396112133905465</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.3695176127720901</v>
+        <v>1.3689039536565999</v>
       </c>
       <c r="B63" s="0">
-        <v>1.09803380968243</v>
+        <v>1.0978798527189</v>
       </c>
       <c r="C63" s="0">
-        <v>1.22793057225008</v>
+        <v>1.2257169102100001</v>
       </c>
       <c r="D63" s="0">
-        <v>1.4038607529725011</v>
+        <v>1.4040190674497637</v>
       </c>
       <c r="E63" s="0">
-        <v>1.1610397317836656</v>
+        <v>1.1607086280634091</v>
       </c>
       <c r="F63" s="0">
-        <v>1.3188329122519369</v>
+        <v>1.3228577369481604</v>
       </c>
       <c r="G63" s="0">
-        <v>-0.033796422926366011</v>
+        <v>-0.034393888472637621</v>
       </c>
       <c r="H63" s="0">
-        <v>-0.062480624280832744</v>
+        <v>-0.062645746616997552</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.091727643442838722</v>
+        <v>-0.09728548574867725</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>1.38089492192831</v>
+        <v>1.3818334622331401</v>
       </c>
       <c r="B64" s="0">
-        <v>1.1118223369950799</v>
+        <v>1.1120168011165299</v>
       </c>
       <c r="C64" s="0">
-        <v>1.2239528440396501</v>
+        <v>1.2231357690706</v>
       </c>
       <c r="D64" s="0">
-        <v>1.4166860735274374</v>
+        <v>1.4169550118474949</v>
       </c>
       <c r="E64" s="0">
-        <v>1.1751863120297565</v>
+        <v>1.1749633912592519</v>
       </c>
       <c r="F64" s="0">
-        <v>1.3311624789410974</v>
+        <v>1.3354702466538479</v>
       </c>
       <c r="G64" s="0">
-        <v>-0.036643045820961825</v>
+        <v>-0.036439937885513647</v>
       </c>
       <c r="H64" s="0">
-        <v>-0.064326564612532083</v>
+        <v>-0.064166589382153125</v>
       </c>
       <c r="I64" s="0">
-        <v>-0.10456322193463177</v>
+        <v>-0.10998192801924662</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>1.39034554214304</v>
+        <v>1.3913139949876301</v>
       </c>
       <c r="B65" s="0">
-        <v>1.12420288973809</v>
+        <v>1.12333803105506</v>
       </c>
       <c r="C65" s="0">
-        <v>1.24784524446429</v>
+        <v>1.2466046694636399</v>
       </c>
       <c r="D65" s="0">
-        <v>1.4293488696357115</v>
+        <v>1.4297198714245878</v>
       </c>
       <c r="E65" s="0">
-        <v>1.1893855007520462</v>
+        <v>1.1892068052500568</v>
       </c>
       <c r="F65" s="0">
-        <v>1.3441192488691436</v>
+        <v>1.3486458880971464</v>
       </c>
       <c r="G65" s="0">
-        <v>-0.037445144991553415</v>
+        <v>-0.037528103169858162</v>
       </c>
       <c r="H65" s="0">
-        <v>-0.065178969876884651</v>
+        <v>-0.065496953320282547</v>
       </c>
       <c r="I65" s="0">
-        <v>-0.097310689621033036</v>
+        <v>-0.10250065914521564</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>1.4064743616933</v>
+        <v>1.4051279588047301</v>
       </c>
       <c r="B66" s="0">
-        <v>1.13767768414666</v>
+        <v>1.13820260765445</v>
       </c>
       <c r="C66" s="0">
-        <v>1.2630017791267301</v>
+        <v>1.26659352512579</v>
       </c>
       <c r="D66" s="0">
-        <v>1.4424638485158625</v>
+        <v>1.4426682071932075</v>
       </c>
       <c r="E66" s="0">
-        <v>1.2036621744020304</v>
+        <v>1.2037024874378872</v>
       </c>
       <c r="F66" s="0">
-        <v>1.3568348398132128</v>
+        <v>1.3617342552709164</v>
       </c>
       <c r="G66" s="0">
-        <v>-0.034904835511956257</v>
+        <v>-0.035542187252212129</v>
       </c>
       <c r="H66" s="0">
-        <v>-0.065054215615064609</v>
+        <v>-0.06494475353040681</v>
       </c>
       <c r="I66" s="0">
-        <v>-0.094893895478702084</v>
+        <v>-0.097130217678929459</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>1.4285047446619801</v>
+        <v>1.4278547804622399</v>
       </c>
       <c r="B67" s="0">
-        <v>1.1548372989835001</v>
+        <v>1.15448341362638</v>
       </c>
       <c r="C67" s="0">
-        <v>1.2655461958765</v>
+        <v>1.2644223603895199</v>
       </c>
       <c r="D67" s="0">
-        <v>1.4557132869588094</v>
+        <v>1.4561034406354123</v>
       </c>
       <c r="E67" s="0">
-        <v>1.2183501541660633</v>
+        <v>1.2184326312586766</v>
       </c>
       <c r="F67" s="0">
-        <v>1.3693111813110033</v>
+        <v>1.3743114514819557</v>
       </c>
       <c r="G67" s="0">
-        <v>-0.028784247485806189</v>
+        <v>-0.029724992933272493</v>
       </c>
       <c r="H67" s="0">
-        <v>-0.064734294085888891</v>
+        <v>-0.064718439101803485</v>
       </c>
       <c r="I67" s="0">
-        <v>-0.1032202078854725</v>
+        <v>-0.10884550014601065</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>1.4430721796511901</v>
+        <v>1.4441238324886401</v>
       </c>
       <c r="B68" s="0">
-        <v>1.1651538714383001</v>
+        <v>1.1660665966899799</v>
       </c>
       <c r="C68" s="0">
-        <v>1.2712905517342601</v>
+        <v>1.2704563649692999</v>
       </c>
       <c r="D68" s="0">
-        <v>1.4688456537836296</v>
+        <v>1.4693044540184941</v>
       </c>
       <c r="E68" s="0">
-        <v>1.2330824955582651</v>
+        <v>1.2333691512253073</v>
       </c>
       <c r="F68" s="0">
-        <v>1.3818603803168141</v>
+        <v>1.387090132397484</v>
       </c>
       <c r="G68" s="0">
-        <v>-0.023744280306654885</v>
+        <v>-0.023706450157305981</v>
       </c>
       <c r="H68" s="0">
-        <v>-0.068108505600720015</v>
+        <v>-0.067324398833399579</v>
       </c>
       <c r="I68" s="0">
-        <v>-0.10996779145020714</v>
+        <v>-0.11585861181094079</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>1.46427941548091</v>
+        <v>1.4652945004709199</v>
       </c>
       <c r="B69" s="0">
-        <v>1.1753919046754999</v>
+        <v>1.17834829979764</v>
       </c>
       <c r="C69" s="0">
-        <v>1.2855800921398299</v>
+        <v>1.28691782129429</v>
       </c>
       <c r="D69" s="0">
-        <v>1.4823480705193257</v>
+        <v>1.4827042307137823</v>
       </c>
       <c r="E69" s="0">
-        <v>1.2481329388470874</v>
+        <v>1.2486418164146782</v>
       </c>
       <c r="F69" s="0">
-        <v>1.3944648597712579</v>
+        <v>1.3999836563715018</v>
       </c>
       <c r="G69" s="0">
-        <v>-0.019436498340497155</v>
+        <v>-0.018823858136869716</v>
       </c>
       <c r="H69" s="0">
-        <v>-0.071213570281566052</v>
+        <v>-0.070438930864112556</v>
       </c>
       <c r="I69" s="0">
-        <v>-0.10958948105101053</v>
+        <v>-0.11399024179476068</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>1.47978074101816</v>
+        <v>1.4782663329452399</v>
       </c>
       <c r="B70" s="0">
-        <v>1.1938271097170701</v>
+        <v>1.1899416284761799</v>
       </c>
       <c r="C70" s="0">
-        <v>1.2966292848379699</v>
+        <v>1.2966915329283399</v>
       </c>
       <c r="D70" s="0">
-        <v>1.4953181062379992</v>
+        <v>1.4959263274310943</v>
       </c>
       <c r="E70" s="0">
-        <v>1.2642452426306641</v>
+        <v>1.2644714195157212</v>
       </c>
       <c r="F70" s="0">
-        <v>1.4070355899574014</v>
+        <v>1.412672100560554</v>
       </c>
       <c r="G70" s="0">
-        <v>-0.017341874660320819</v>
+        <v>-0.018784608254001762</v>
       </c>
       <c r="H70" s="0">
-        <v>-0.070950880156086832</v>
+        <v>-0.073163580685796537</v>
       </c>
       <c r="I70" s="0">
-        <v>-0.10991995550808596</v>
+        <v>-0.11557328081900754</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>1.4909632129432999</v>
+        <v>1.49042557842001</v>
       </c>
       <c r="B71" s="0">
-        <v>1.21072517501593</v>
+        <v>1.2104761605978001</v>
       </c>
       <c r="C71" s="0">
-        <v>1.3114470857665601</v>
+        <v>1.3109339324726701</v>
       </c>
       <c r="D71" s="0">
-        <v>1.5079330589702733</v>
+        <v>1.508565049384305</v>
       </c>
       <c r="E71" s="0">
-        <v>1.2808710281238351</v>
+        <v>1.2814127009258471</v>
       </c>
       <c r="F71" s="0">
-        <v>1.4196742970556167</v>
+        <v>1.4255098952467153</v>
       </c>
       <c r="G71" s="0">
-        <v>-0.018247572788904608</v>
+        <v>-0.019652337629099893</v>
       </c>
       <c r="H71" s="0">
-        <v>-0.069560706487962032</v>
+        <v>-0.070617814705653009</v>
       </c>
       <c r="I71" s="0">
-        <v>-0.10815869172368901</v>
+        <v>-0.11443795496000805</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>1.49984367830329</v>
+        <v>1.5009008957147001</v>
       </c>
       <c r="B72" s="0">
-        <v>1.23182321356859</v>
+        <v>1.23322254998201</v>
       </c>
       <c r="C72" s="0">
-        <v>1.32565091485883</v>
+        <v>1.3251442663325901</v>
       </c>
       <c r="D72" s="0">
-        <v>1.5200578251945298</v>
+        <v>1.5207368102869714</v>
       </c>
       <c r="E72" s="0">
-        <v>1.2981156905273192</v>
+        <v>1.2989943975516447</v>
       </c>
       <c r="F72" s="0">
-        <v>1.4323190221730089</v>
+        <v>1.4383588984438351</v>
       </c>
       <c r="G72" s="0">
-        <v>-0.019500558228226089</v>
+        <v>-0.019629991954263733</v>
       </c>
       <c r="H72" s="0">
-        <v>-0.06654652424634</v>
+        <v>-0.066100264187982663</v>
       </c>
       <c r="I72" s="0">
-        <v>-0.1080979754470173</v>
+        <v>-0.11473164296018273</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>1.5127370002359799</v>
+        <v>1.51377939323426</v>
       </c>
       <c r="B73" s="0">
-        <v>1.2521471493017999</v>
+        <v>1.25498972208854</v>
       </c>
       <c r="C73" s="0">
-        <v>1.3272525621612601</v>
+        <v>1.32590589119131</v>
       </c>
       <c r="D73" s="0">
-        <v>1.5323888223679261</v>
+        <v>1.5330151610613856</v>
       </c>
       <c r="E73" s="0">
-        <v>1.3154121745757696</v>
+        <v>1.3165215100983412</v>
       </c>
       <c r="F73" s="0">
-        <v>1.4445526856685988</v>
+        <v>1.4507806500118139</v>
       </c>
       <c r="G73" s="0">
-        <v>-0.019476360733900362</v>
+        <v>-0.019159749738383566</v>
       </c>
       <c r="H73" s="0">
-        <v>-0.065507565772509935</v>
+        <v>-0.065410878022942653</v>
       </c>
       <c r="I73" s="0">
-        <v>-0.1148412668938536</v>
+        <v>-0.12189512297985901</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>1.5258600212476701</v>
+        <v>1.5241260507235199</v>
       </c>
       <c r="B74" s="0">
-        <v>1.2632861356226699</v>
+        <v>1.25913989433427</v>
       </c>
       <c r="C74" s="0">
-        <v>1.3537103747399599</v>
+        <v>1.3554059892179799</v>
       </c>
       <c r="D74" s="0">
-        <v>1.5448986313390054</v>
+        <v>1.5457357777830669</v>
       </c>
       <c r="E74" s="0">
-        <v>1.332526885127191</v>
+        <v>1.3333930241089786</v>
       </c>
       <c r="F74" s="0">
-        <v>1.4571436016788903</v>
+        <v>1.4635610875245766</v>
       </c>
       <c r="G74" s="0">
-        <v>-0.01857702526409977</v>
+        <v>-0.020200454814704165</v>
       </c>
       <c r="H74" s="0">
-        <v>-0.066840532724018145</v>
+        <v>-0.069777579955921751</v>
       </c>
       <c r="I74" s="0">
-        <v>-0.10477425892048077</v>
+        <v>-0.11018790625068042</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>1.5415101312302699</v>
+        <v>1.5412429887936401</v>
       </c>
       <c r="B75" s="0">
-        <v>1.2876029783588201</v>
+        <v>1.28734203605394</v>
       </c>
       <c r="C75" s="0">
-        <v>1.37221273372257</v>
+        <v>1.3721374566423901</v>
       </c>
       <c r="D75" s="0">
-        <v>1.5571099022547221</v>
+        <v>1.5580079093686963</v>
       </c>
       <c r="E75" s="0">
-        <v>1.3508250672861715</v>
+        <v>1.3520489364453925</v>
       </c>
       <c r="F75" s="0">
-        <v>1.4695602289393825</v>
+        <v>1.476122318164639</v>
       </c>
       <c r="G75" s="0">
-        <v>-0.014880332518482085</v>
+        <v>-0.016315228757070636</v>
       </c>
       <c r="H75" s="0">
-        <v>-0.063481038888622165</v>
+        <v>-0.065300072797187636</v>
       </c>
       <c r="I75" s="0">
-        <v>-0.097800633927939196</v>
+        <v>-0.10412649462962062</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>1.55867107367192</v>
+        <v>1.55965805245959</v>
       </c>
       <c r="B76" s="0">
-        <v>1.30915037387235</v>
+        <v>1.3108994649197701</v>
       </c>
       <c r="C76" s="0">
-        <v>1.38660259672222</v>
+        <v>1.38674098535066</v>
       </c>
       <c r="D76" s="0">
-        <v>1.5695464089780404</v>
+        <v>1.5705080889555938</v>
       </c>
       <c r="E76" s="0">
-        <v>1.3696672106411727</v>
+        <v>1.3712476046612525</v>
       </c>
       <c r="F76" s="0">
-        <v>1.4817887444605693</v>
+        <v>1.4885429221426638</v>
       </c>
       <c r="G76" s="0">
-        <v>-0.010880451380791266</v>
+        <v>-0.011138165251069717</v>
       </c>
       <c r="H76" s="0">
-        <v>-0.059503344110534935</v>
+        <v>-0.060239349360543419</v>
       </c>
       <c r="I76" s="0">
-        <v>-0.094648579446601044</v>
+        <v>-0.10142119204727459</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>1.5818625672665501</v>
+        <v>1.5828782652768001</v>
       </c>
       <c r="B77" s="0">
-        <v>1.33528068641355</v>
+        <v>1.33428884889031</v>
       </c>
       <c r="C77" s="0">
-        <v>1.4080701798435</v>
+        <v>1.4064093206037001</v>
       </c>
       <c r="D77" s="0">
-        <v>1.5816339463824012</v>
+        <v>1.582796714774193</v>
       </c>
       <c r="E77" s="0">
-        <v>1.3892168713016493</v>
+        <v>1.3908570415431945</v>
       </c>
       <c r="F77" s="0">
-        <v>1.4941529680081009</v>
+        <v>1.5010107026793422</v>
       </c>
       <c r="G77" s="0">
-        <v>-0.011083662313722433</v>
+        <v>-0.011894572672353077</v>
       </c>
       <c r="H77" s="0">
-        <v>-0.05560021229347397</v>
+        <v>-0.057707362938796344</v>
       </c>
       <c r="I77" s="0">
-        <v>-0.086598577970832147</v>
+        <v>-0.094738162211547919</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>1.5579343668215999</v>
+        <v>1.55602003501801</v>
       </c>
       <c r="B78" s="0">
-        <v>1.35293583018199</v>
+        <v>1.35235033097584</v>
       </c>
       <c r="C78" s="0">
-        <v>1.42767164595096</v>
+        <v>1.4285906284527199</v>
       </c>
       <c r="D78" s="0">
-        <v>1.5918424724047533</v>
+        <v>1.5929349244693485</v>
       </c>
       <c r="E78" s="0">
-        <v>1.4090820145172795</v>
+        <v>1.4109885455142446</v>
       </c>
       <c r="F78" s="0">
-        <v>1.5066704177169989</v>
+        <v>1.5137700088789221</v>
       </c>
       <c r="G78" s="0">
-        <v>-0.023383661494306599</v>
+        <v>-0.025240802671288518</v>
       </c>
       <c r="H78" s="0">
-        <v>-0.055810434124901095</v>
+        <v>-0.058294418789742897</v>
       </c>
       <c r="I78" s="0">
-        <v>-0.077333166543512605</v>
+        <v>-0.083888759074386254</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>1.57725478498591</v>
+        <v>1.57727048133451</v>
       </c>
       <c r="B79" s="0">
-        <v>1.37916339800891</v>
+        <v>1.37907068769675</v>
       </c>
       <c r="C79" s="0">
-        <v>1.4701939519578799</v>
+        <v>1.4705885621696599</v>
       </c>
       <c r="D79" s="0">
-        <v>1.6039099975697457</v>
+        <v>1.6052132932776091</v>
       </c>
       <c r="E79" s="0">
-        <v>1.4288477860394446</v>
+        <v>1.4310067221331477</v>
       </c>
       <c r="F79" s="0">
-        <v>1.519316832387235</v>
+        <v>1.5265452971876705</v>
       </c>
       <c r="G79" s="0">
-        <v>-0.025596683693533625</v>
+        <v>-0.027274733185730454</v>
       </c>
       <c r="H79" s="0">
-        <v>-0.048829940335244786</v>
+        <v>-0.05075323307142246</v>
       </c>
       <c r="I79" s="0">
-        <v>-0.049975083671277863</v>
+        <v>-0.056684598781173538</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>1.5971047101623199</v>
+        <v>1.5980048540113301</v>
       </c>
       <c r="B80" s="0">
-        <v>1.41149836398978</v>
+        <v>1.4132533923350901</v>
       </c>
       <c r="C80" s="0">
-        <v>1.5053485717861701</v>
+        <v>1.5060581515834099</v>
       </c>
       <c r="D80" s="0">
-        <v>1.6161588425486988</v>
+        <v>1.6175237061438976</v>
       </c>
       <c r="E80" s="0">
-        <v>1.4490348027668765</v>
+        <v>1.4515752250563816</v>
       </c>
       <c r="F80" s="0">
-        <v>1.5318438503913441</v>
+        <v>1.5392584325060938</v>
       </c>
       <c r="G80" s="0">
-        <v>-0.021119256288850863</v>
+        <v>-0.021812103916382115</v>
       </c>
       <c r="H80" s="0">
-        <v>-0.039627768641892415</v>
+        <v>-0.040641467028098517</v>
       </c>
       <c r="I80" s="0">
-        <v>-0.027060067868350163</v>
+        <v>-0.033647131644071307</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>1.6089675199354001</v>
+        <v>1.60993305975353</v>
       </c>
       <c r="B81" s="0">
-        <v>1.43093875155173</v>
+        <v>1.43317037320872</v>
       </c>
       <c r="C81" s="0">
-        <v>1.52719618697718</v>
+        <v>1.52825400631096</v>
       </c>
       <c r="D81" s="0">
-        <v>1.6285340720273744</v>
+        <v>1.6299345168759252</v>
       </c>
       <c r="E81" s="0">
-        <v>1.4689689335089398</v>
+        <v>1.471760736965861</v>
       </c>
       <c r="F81" s="0">
-        <v>1.5441484870764985</v>
+        <v>1.5517533337774889</v>
       </c>
       <c r="G81" s="0">
-        <v>-0.019816054388349519</v>
+        <v>-0.020417552530149256</v>
       </c>
       <c r="H81" s="0">
-        <v>-0.035667396327130979</v>
+        <v>-0.037455376010057759</v>
       </c>
       <c r="I81" s="0">
-        <v>-0.016963146276421599</v>
+        <v>-0.023900517002665912</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>1.6218788822326999</v>
+        <v>1.6198615529984299</v>
       </c>
       <c r="B82" s="0">
-        <v>1.46206365357587</v>
+        <v>1.4581000769938901</v>
       </c>
       <c r="C82" s="0">
-        <v>1.54554164045524</v>
+        <v>1.54278063396795</v>
       </c>
       <c r="D82" s="0">
-        <v>1.640435228874134</v>
+        <v>1.6421369157198269</v>
       </c>
       <c r="E82" s="0">
-        <v>1.4898830334687212</v>
+        <v>1.4925548829807345</v>
       </c>
       <c r="F82" s="0">
-        <v>1.5566146570858961</v>
+        <v>1.5642504286965853</v>
       </c>
       <c r="G82" s="0">
-        <v>-0.018705910542903485</v>
+        <v>-0.021487265772971508</v>
       </c>
       <c r="H82" s="0">
-        <v>-0.028617947267056017</v>
+        <v>-0.033463387325767181</v>
       </c>
       <c r="I82" s="0">
-        <v>-0.011134687670726754</v>
+        <v>-0.020982812261934703</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>1.6334034597639899</v>
+        <v>1.6336451788750599</v>
       </c>
       <c r="B83" s="0">
-        <v>1.48975783219646</v>
+        <v>1.48987660319217</v>
       </c>
       <c r="C83" s="0">
-        <v>1.56197288089474</v>
+        <v>1.5628770125056699</v>
       </c>
       <c r="D83" s="0">
-        <v>1.6525704874660723</v>
+        <v>1.6543669383063113</v>
       </c>
       <c r="E83" s="0">
-        <v>1.51082573153471</v>
+        <v>1.5139696665510152</v>
       </c>
       <c r="F83" s="0">
-        <v>1.5690811345731366</v>
+        <v>1.5769707102901078</v>
       </c>
       <c r="G83" s="0">
-        <v>-0.018033293881745665</v>
+        <v>-0.020240653949926926</v>
       </c>
       <c r="H83" s="0">
-        <v>-0.022247246246539502</v>
+        <v>-0.025606787888936441</v>
       </c>
       <c r="I83" s="0">
-        <v>-0.0064541506712527908</v>
+        <v>-0.013781674023882286</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>1.6489594454266601</v>
+        <v>1.6498486686373901</v>
       </c>
       <c r="B84" s="0">
-        <v>1.51444819291835</v>
+        <v>1.51622118197807</v>
       </c>
       <c r="C84" s="0">
-        <v>1.58623028848825</v>
+        <v>1.58716654801049</v>
       </c>
       <c r="D84" s="0">
-        <v>1.6652160403205176</v>
+        <v>1.6671013477088257</v>
       </c>
       <c r="E84" s="0">
-        <v>1.5316130229266238</v>
+        <v>1.5352057777360926</v>
       </c>
       <c r="F84" s="0">
-        <v>1.5816706171258661</v>
+        <v>1.5897425175277695</v>
       </c>
       <c r="G84" s="0">
-        <v>-0.016185274590571022</v>
+        <v>-0.017343762983123255</v>
       </c>
       <c r="H84" s="0">
-        <v>-0.015928582226694472</v>
+        <v>-0.018092972440912351</v>
       </c>
       <c r="I84" s="0">
-        <v>0.0041174253341111659</v>
+        <v>-0.0030158973201688402</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>1.6671645204110701</v>
+        <v>1.6679617240153899</v>
       </c>
       <c r="B85" s="0">
-        <v>1.54688657513751</v>
+        <v>1.5486256810007999</v>
       </c>
       <c r="C85" s="0">
-        <v>1.61086504978125</v>
+        <v>1.61049019971118</v>
       </c>
       <c r="D85" s="0">
-        <v>1.6778081485285501</v>
+        <v>1.6797980477791317</v>
       </c>
       <c r="E85" s="0">
-        <v>1.5530429432836828</v>
+        <v>1.5568900436790736</v>
       </c>
       <c r="F85" s="0">
-        <v>1.5943543713151831</v>
+        <v>1.6025737999512173</v>
       </c>
       <c r="G85" s="0">
-        <v>-0.0095982352289063454</v>
+        <v>-0.010888708356723986</v>
       </c>
       <c r="H85" s="0">
-        <v>-0.0051671625274306281</v>
+        <v>-0.0083172318687147993</v>
       </c>
       <c r="I85" s="0">
-        <v>0.016596532222130964</v>
+        <v>0.0080148351924369948</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>1.69286623850083</v>
+        <v>1.69084299300411</v>
       </c>
       <c r="B86" s="0">
-        <v>1.5851714771568901</v>
+        <v>1.58139671527604</v>
       </c>
       <c r="C86" s="0">
-        <v>1.6389913729777801</v>
+        <v>1.6371653656795899</v>
       </c>
       <c r="D86" s="0">
-        <v>1.6905024193752909</v>
+        <v>1.6927984441809405</v>
       </c>
       <c r="E86" s="0">
-        <v>1.5748976500282674</v>
+        <v>1.5786925198133788</v>
       </c>
       <c r="F86" s="0">
-        <v>1.6071807241068399</v>
+        <v>1.615490134990458</v>
       </c>
       <c r="G86" s="0">
-        <v>0.0031391132501172002</v>
+        <v>-0.00014744236739055319</v>
       </c>
       <c r="H86" s="0">
-        <v>0.0076233619917400099</v>
+        <v>0.0017487036038374086</v>
       </c>
       <c r="I86" s="0">
-        <v>0.032154318342003399</v>
+        <v>0.022269638992965857</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>1.7195769506076599</v>
+        <v>1.72001401090748</v>
       </c>
       <c r="B87" s="0">
-        <v>1.6079608592808901</v>
+        <v>1.60857586545749</v>
       </c>
       <c r="C87" s="0">
-        <v>1.6685132689637201</v>
+        <v>1.66986041664887</v>
       </c>
       <c r="D87" s="0">
-        <v>1.703917015118658</v>
+        <v>1.7063790886000905</v>
       </c>
       <c r="E87" s="0">
-        <v>1.5960079700408425</v>
+        <v>1.6002928004828483</v>
       </c>
       <c r="F87" s="0">
-        <v>1.6199384626014732</v>
+        <v>1.6284866782444887</v>
       </c>
       <c r="G87" s="0">
-        <v>0.014344709595039768</v>
+        <v>0.011650583721481917</v>
       </c>
       <c r="H87" s="0">
-        <v>0.013805213544763065</v>
+        <v>0.009478151032418447</v>
       </c>
       <c r="I87" s="0">
-        <v>0.048191366808720826</v>
+        <v>0.04065344346651191</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>1.73876552187888</v>
+        <v>1.7396311861863401</v>
       </c>
       <c r="B88" s="0">
-        <v>1.63758798345579</v>
+        <v>1.6391269698805799</v>
       </c>
       <c r="C88" s="0">
-        <v>1.69392752243158</v>
+        <v>1.6946983073928901</v>
       </c>
       <c r="D88" s="0">
-        <v>1.7167507686307739</v>
+        <v>1.7194421594533478</v>
       </c>
       <c r="E88" s="0">
-        <v>1.6177197261973839</v>
+        <v>1.6224151388691841</v>
       </c>
       <c r="F88" s="0">
-        <v>1.6327961636639086</v>
+        <v>1.6414929069982866</v>
       </c>
       <c r="G88" s="0">
-        <v>0.021672777472750055</v>
+        <v>0.019801974736849928</v>
       </c>
       <c r="H88" s="0">
-        <v>0.019337917465995537</v>
+        <v>0.016173398111865106</v>
       </c>
       <c r="I88" s="0">
-        <v>0.061202341701673206</v>
+        <v>0.053417280800223704</v>
       </c>
     </row>
   </sheetData>
